--- a/backend/data/financials_by_company/0QYI.L.xlsx
+++ b/backend/data/financials_by_company/0QYI.L.xlsx
@@ -3827,172 +3827,172 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>prevName</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>nameChangeDate</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>shortName</t>
         </is>
       </c>
       <c r="EI1" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Wilmot Reed Hastings Jr.', 'age': 65, 'title': 'Co-Founder &amp; Chairman', 'yearBorn': 1960, 'fiscalYear': 2025, 'totalPay': 117178, 'exercisedValue': 370039264, 'unexercisedValue': 1205574656}, {'maxAge': 1, 'name': 'Mr. Theodore A. Sarandos', 'age': 60, 'title': 'Co-CEO, President &amp; Director', 'yearBorn': 1965, 'fiscalYear': 2025, 'totalPay': 12507548, 'exercisedValue': 173482848, 'unexercisedValue': 299971392}, {'maxAge': 1, 'name': 'Mr. Gregory K. Peters', 'age': 54, 'title': 'Co-CEO, President &amp; Director', 'yearBorn': 1971, 'fiscalYear': 2025, 'totalPay': 11788883, 'exercisedValue': 89372000, 'unexercisedValue': 143010080}, {'maxAge': 1, 'name': 'Mr. Spencer Adam Neumann', 'age': 55, 'title': 'Chief Financial Officer', 'yearBorn': 1970, 'fiscalYear': 2025, 'totalPay': 6811618, 'exercisedValue': 25442484, 'unexercisedValue': 95993752}, {'maxAge': 1, 'name': 'Mr. David  Hyman J.D.', 'age': 59, 'title': 'Chief Legal Officer &amp; Secretary', 'yearBorn': 1966, 'fiscalYear': 2025, 'totalPay': 6719773, 'exercisedValue': 90937936, 'unexercisedValue': 14241332}, {'maxAge': 1, 'name': 'Mr. Clete  Willems', 'age': 45, 'title': 'Chief Global Affairs Officer', 'yearBorn': 1980, 'fiscalYear': 2025, 'totalPay': 5468564, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Natalie  Gutteridge', 'title': 'VP of Corporate Legal &amp; Operations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jeffrey William Karbowski', 'age': 46, 'title': 'Chief Accounting Officer', 'yearBorn': 1979, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Elizabeth  Stone', 'title': 'Chief Product &amp; Technology Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Spencer  Wang', 'title': 'Vice President of Finance, Corporate Development &amp; Investor Relations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Spencer Adam Neumann', 'age': 55, 'title': 'Chief Financial Officer', 'yearBorn': 1970, 'fiscalYear': 2025, 'totalPay': 6811618, 'exercisedValue': 25442484, 'unexercisedValue': 95993752}, {'maxAge': 1, 'name': 'Mr. David  Hyman J.D.', 'age': 59, 'title': 'Chief Legal Officer &amp; Secretary', 'yearBorn': 1966, 'fiscalYear': 2025, 'totalPay': 6719773, 'exercisedValue': 90937936, 'unexercisedValue': 14241332}, {'maxAge': 1, 'name': 'Mr. Clete  Willems', 'age': 45, 'title': 'Chief Global Affairs Officer', 'yearBorn': 1980, 'fiscalYear': 2025, 'totalPay': 5468564, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Natalie  Gutteridge', 'title': 'VP of Corporate Legal &amp; Operations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jeffrey William Karbowski', 'age': 46, 'title': 'Chief Accounting Officer', 'yearBorn': 1979, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Elizabeth  Stone', 'title': 'Chief Product &amp; Technology Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Spencer  Wang', 'title': 'Vice President of Finance, Corporate Development &amp; Investor Relations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Dani  Dudeck', 'title': 'Chief Communications Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Marian  Lee', 'age': 45, 'title': 'Chief Marketing Officer', 'yearBorn': 1980, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Bela  Bajaria', 'age': 53, 'title': 'Chief Content Officer', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -4110,7 +4110,7 @@
         <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="U2" t="n">
         <v>1767139200</v>
@@ -4127,40 +4127,40 @@
         <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>86.84999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>85.68000000000001</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>83.45</v>
+        <v>71.8117</v>
       </c>
       <c r="AB2" t="n">
-        <v>86</v>
+        <v>77.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>86.84999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>85.68000000000001</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="AE2" t="n">
-        <v>83.45</v>
+        <v>71.8117</v>
       </c>
       <c r="AF2" t="n">
-        <v>86</v>
+        <v>77.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.548</v>
+        <v>1.491</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.968765</v>
+        <v>3.4306674</v>
       </c>
       <c r="AI2" t="n">
-        <v>146959</v>
+        <v>304473</v>
       </c>
       <c r="AJ2" t="n">
-        <v>146959</v>
+        <v>304473</v>
       </c>
       <c r="AK2" t="n">
         <v>7596</v>
@@ -4175,13 +4175,13 @@
         <v>1180</v>
       </c>
       <c r="AO2" t="n">
-        <v>35913297920</v>
+        <v>31044059136</v>
       </c>
       <c r="AP2" t="n">
-        <v>361497053628</v>
+        <v>325831590096</v>
       </c>
       <c r="AQ2" t="n">
-        <v>83.45</v>
+        <v>71.8117</v>
       </c>
       <c r="AR2" t="n">
         <v>1088</v>
@@ -4193,7 +4193,7 @@
         <v>51.97898</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.7659054</v>
+        <v>0.6620615</v>
       </c>
       <c r="AV2" t="n">
         <v>951.4</v>
@@ -4216,7 +4216,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>357064638464</v>
+        <v>331366596608</v>
       </c>
       <c r="BC2" t="n">
         <v>0.28521</v>
@@ -4231,7 +4231,7 @@
         <v>0.00567</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.85007006</v>
+        <v>0.85103</v>
       </c>
       <c r="BH2" t="n">
         <v>428252992</v>
@@ -4240,7 +4240,7 @@
         <v>7.389</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11.349303</v>
+        <v>9.810529000000001</v>
       </c>
       <c r="BK2" t="n">
         <v>1767139200</v>
@@ -4269,16 +4269,16 @@
         <v>1763337600</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.615</v>
+        <v>7.067</v>
       </c>
       <c r="BT2" t="n">
-        <v>24.99</v>
+        <v>23.191</v>
       </c>
       <c r="BU2" t="n">
         <v>0.61920536</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="BX2" t="n">
-        <v>83.86</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
@@ -4388,128 +4388,128 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DA2" t="n">
-        <v>-2.9899979</v>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>POSTPOST</t>
+        </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>83.45 - 86.0</t>
+          <t>NETFLIX INC NETFLIX ORD</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>-6.5850525</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>72.48999999999999</v>
+      </c>
+      <c r="DF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1415174400000</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-5.1100006</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>71.8117 - 77.7</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
           <t>LSE</t>
         </is>
       </c>
-      <c r="DD2" t="n">
+      <c r="DK2" t="n">
         <v>7596</v>
       </c>
-      <c r="DE2" t="n">
-        <v>0.41000366</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>0.0049131657</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>83.45 - 1088.0</t>
-        </is>
-      </c>
-      <c r="DH2" t="n">
-        <v>-1004.14</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>-0.9229228</v>
-      </c>
-      <c r="DJ2" t="n">
+      <c r="DL2" t="n">
+        <v>0.67829895</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0.009445522</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>71.8117 - 1088.0</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>-1015.51</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.93337315</v>
+      </c>
+      <c r="DQ2" t="n">
         <v>61.920536</v>
       </c>
-      <c r="DK2" t="n">
-        <v>1776353400</v>
-      </c>
-      <c r="DL2" t="n">
+      <c r="DR2" t="n">
         <v>1784215800</v>
       </c>
-      <c r="DM2" t="n">
+      <c r="DS2" t="n">
         <v>1784215800</v>
       </c>
-      <c r="DN2" t="n">
-        <v>1776372300</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1776372300</v>
-      </c>
-      <c r="DP2" t="b">
-        <v>1</v>
-      </c>
-      <c r="DQ2" t="n">
+      <c r="DT2" t="n">
+        <v>1784215800</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1784215800</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1784215800</v>
+      </c>
+      <c r="DW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
         <v>21.13</v>
       </c>
-      <c r="DR2" t="n">
-        <v>-867.54004</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.91185623</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-579.8225</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.8736444</v>
-      </c>
-      <c r="DV2" t="n">
+      <c r="DY2" t="n">
+        <v>-878.91003</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.923807</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-591.1925</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.8907761</v>
+      </c>
+      <c r="EC2" t="n">
         <v>15</v>
       </c>
-      <c r="DW2" t="n">
+      <c r="ED2" t="n">
         <v>15</v>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="EE2" t="inlineStr">
         <is>
           <t>VIVEK</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="DZ2" t="b">
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="EG2" t="b">
         <v>0</v>
       </c>
-      <c r="EA2" t="n">
-        <v>1415174400000</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-3.4427152</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>83.86</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>Netflix, Inc.</t>
-        </is>
-      </c>
-      <c r="EE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>NETFLIX INC NETFLIX ORD</t>
-        </is>
-      </c>
       <c r="EI2" t="n">
-        <v>1780424099</v>
+        <v>1782150220</v>
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>0</v>
       </c>
       <c r="EQ2" t="n">
-        <v>1.6922</v>
+        <v>1.5242</v>
       </c>
     </row>
   </sheetData>
